--- a/data/trans_dic/IP22D2_R_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP22D2_R_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,15</t>
+          <t>0,0; 20,49</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,01</t>
+          <t>0,0; 15,77</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>618</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3425</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2975</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3484</t>
+          <t>0; 3199</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2701</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2885</t>
+          <t>0; 2240</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>618</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1068</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 3397</t>
+          <t>0; 2073</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 3825</t>
+          <t>0; 3710</t>
         </is>
       </c>
     </row>
